--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerIdenInfo_export.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/SalerIdenInfo_export.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\BS3.0feature-3.0.4运营\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\tams-3.0.7运营\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>*销售机构代码</t>
   </si>
@@ -107,6 +107,10 @@
   </si>
   <si>
     <t>错误信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>*销售人员登记编码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -503,31 +507,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="13" style="2" customWidth="1"/>
-    <col min="3" max="3" width="7.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.625" customWidth="1"/>
-    <col min="5" max="5" width="12.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.875" customWidth="1"/>
-    <col min="7" max="7" width="13" style="2" customWidth="1"/>
-    <col min="8" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="10.875" customWidth="1"/>
-    <col min="11" max="11" width="22.5" style="2" customWidth="1"/>
-    <col min="12" max="13" width="9" style="2"/>
-    <col min="16" max="16" width="17.25" style="2" customWidth="1"/>
-    <col min="17" max="18" width="21.375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="21" style="2" customWidth="1"/>
-    <col min="21" max="21" width="21.375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="19.25" customWidth="1"/>
-    <col min="23" max="23" width="11.75" style="2" customWidth="1"/>
-    <col min="24" max="26" width="9" style="2"/>
-    <col min="28" max="28" width="13.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.625" customWidth="1"/>
+    <col min="6" max="6" width="12.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
+    <col min="8" max="8" width="13" style="2" customWidth="1"/>
+    <col min="9" max="10" width="9" style="2"/>
+    <col min="11" max="11" width="10.875" customWidth="1"/>
+    <col min="12" max="12" width="22.5" style="2" customWidth="1"/>
+    <col min="13" max="14" width="9" style="2"/>
+    <col min="17" max="17" width="17.25" style="2" customWidth="1"/>
+    <col min="18" max="19" width="21.375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="13" customWidth="1"/>
+    <col min="21" max="21" width="21" style="2" customWidth="1"/>
+    <col min="22" max="22" width="21.375" style="2" customWidth="1"/>
+    <col min="23" max="23" width="19.25" customWidth="1"/>
+    <col min="24" max="24" width="11.75" style="2" customWidth="1"/>
+    <col min="25" max="27" width="9" style="2"/>
+    <col min="29" max="29" width="13.375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:30" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
@@ -535,129 +540,123 @@
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.15">
-      <c r="J18" s="7"/>
+    <row r="18" spans="11:11" x14ac:dyDescent="0.15">
+      <c r="K18" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576">
+  <dataValidations count="11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
       <formula1>"01 高中,02 大专,03 本科,04 硕士研究生,05 博士研究生,99 其他"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="时间必须具体到日，如19860513" sqref="E2:E1048576"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="时间必须具体到日，如19860513" sqref="F2:F1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576">
       <formula1>"01 男,02 女"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>"01 居民身份证,02 外国护照,03 港澳往来内地通行证,04 台湾往来内地通行证,05 外国人永久居留证,99 其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
       <formula1>"01 学士,02 硕士,03 博士,99 其他"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="时间必须具体到月，如200012" sqref="P2:R1048576"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="时间必须具体到月，如200012" sqref="Q2:S1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T1048576">
       <formula1>"01 初级,02 中级,03 高级,99 其他"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="请参照“各要素输入规则”中的具体要求填写" sqref="T2:T1048576 V2:V1048576"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA2:AA1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="请参照“各要素输入规则”中的具体要求填写" sqref="U2:U1048576 W2:W1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>"01 正常,02 转岗,03 停职,04 离职"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:F1 J1 N1:T1 V1 AA1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:G1 K1 O1:U1 W1 AB1"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576">
+      <formula1>#REF!</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>